--- a/Team-Data/2014-15/3-21-2014-15.xlsx
+++ b/Team-Data/2014-15/3-21-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -763,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
         <v>7</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -811,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-0.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
         <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
         <v>19</v>
@@ -957,7 +1024,7 @@
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
@@ -966,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -981,13 +1048,13 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.426</v>
+        <v>0.418</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.328</v>
+        <v>0.326</v>
       </c>
       <c r="O4" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
         <v>31.9</v>
       </c>
       <c r="T4" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
         <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1088,28 +1155,28 @@
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z4" t="n">
         <v>19.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
@@ -1121,10 +1188,10 @@
         <v>19</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1136,28 +1203,28 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR4" t="n">
         <v>22</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>23</v>
       </c>
       <c r="AS4" t="n">
         <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
@@ -1336,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,10 +1415,10 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1456,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
         <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J6" t="n">
         <v>83.09999999999999</v>
@@ -1419,7 +1486,7 @@
         <v>22.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O6" t="n">
         <v>19.9</v>
@@ -1449,34 +1516,34 @@
         <v>6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
         <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1509,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1530,10 +1597,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -1652,16 +1719,16 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1670,7 +1737,7 @@
         <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1691,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>22</v>
@@ -1700,10 +1767,10 @@
         <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>19</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" t="n">
         <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.638</v>
+        <v>0.629</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,10 +1838,10 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L8" t="n">
         <v>9.300000000000001</v>
@@ -1783,7 +1850,7 @@
         <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
         <v>16.7</v>
@@ -1792,22 +1859,22 @@
         <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
@@ -1822,28 +1889,28 @@
         <v>19.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,7 +1928,7 @@
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>18</v>
@@ -1873,10 +1940,10 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -2025,13 +2092,13 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="n">
         <v>17</v>
       </c>
-      <c r="AI9" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
@@ -2058,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2082,7 +2149,7 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L10" t="n">
         <v>8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P10" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0.709</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S10" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T10" t="n">
         <v>45.3</v>
       </c>
       <c r="U10" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>7.7</v>
@@ -2180,22 +2247,22 @@
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
         <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,10 +2274,10 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ10" t="n">
         <v>6</v>
@@ -2249,13 +2316,13 @@
         <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2267,7 +2334,7 @@
         <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="J11" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.478</v>
@@ -2326,7 +2393,7 @@
         <v>10.6</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N11" t="n">
         <v>0.393</v>
@@ -2338,7 +2405,7 @@
         <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R11" t="n">
         <v>10.2</v>
@@ -2347,7 +2414,7 @@
         <v>34.2</v>
       </c>
       <c r="T11" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U11" t="n">
         <v>27.3</v>
@@ -2365,19 +2432,19 @@
         <v>3.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA11" t="n">
         <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.7</v>
+        <v>109.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -2484,22 +2551,22 @@
         <v>68</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.662</v>
+        <v>0.676</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2511,55 +2578,55 @@
         <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
         <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2577,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
@@ -2616,25 +2683,25 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>0.435</v>
+        <v>0.441</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>7.1</v>
@@ -2693,37 +2760,37 @@
         <v>20.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
         <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R13" t="n">
         <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U13" t="n">
         <v>21.4</v>
       </c>
       <c r="V13" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y13" t="n">
         <v>4.9</v>
@@ -2732,34 +2799,34 @@
         <v>20.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2774,16 +2841,16 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2938,16 +3005,16 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
@@ -2959,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.258</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>5</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
@@ -3135,22 +3202,22 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
       </c>
       <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS15" t="n">
         <v>13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>11</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -3171,13 +3238,13 @@
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>0.696</v>
       </c>
       <c r="H16" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I16" t="n">
         <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K16" t="n">
         <v>0.458</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O16" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
@@ -3263,10 +3330,10 @@
         <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
@@ -3284,10 +3351,10 @@
         <v>99</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,10 +3372,10 @@
         <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,22 +3384,22 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3350,7 +3417,7 @@
         <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3499,10 +3566,10 @@
         <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
@@ -3544,7 +3611,7 @@
         <v>26</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3666,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
@@ -3684,7 +3751,7 @@
         <v>4</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
         <v>25</v>
@@ -3696,10 +3763,10 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT18" t="n">
         <v>23</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>22</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3723,10 +3790,10 @@
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3848,13 +3915,13 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
         <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>0.529</v>
+        <v>0.536</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,49 +4022,49 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O20" t="n">
         <v>16.7</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
@@ -4006,19 +4073,19 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
@@ -4045,37 +4112,37 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR20" t="n">
         <v>9</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4215,7 +4282,7 @@
         <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4251,13 +4318,13 @@
         <v>18</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4397,7 +4464,7 @@
         <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK22" t="n">
         <v>19</v>
@@ -4415,10 +4482,10 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>0.314</v>
+        <v>0.31</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4504,16 +4571,16 @@
         <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O23" t="n">
         <v>14.2</v>
@@ -4522,19 +4589,19 @@
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.8</v>
@@ -4543,25 +4610,25 @@
         <v>7.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA23" t="n">
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,13 +4673,13 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AV23" t="n">
         <v>21</v>
@@ -4621,13 +4688,13 @@
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>27</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.529</v>
+        <v>0.522</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J25" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.455</v>
@@ -4874,10 +4941,10 @@
         <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O25" t="n">
         <v>16.7</v>
@@ -4886,7 +4953,7 @@
         <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R25" t="n">
         <v>11.1</v>
@@ -4895,7 +4962,7 @@
         <v>32.3</v>
       </c>
       <c r="T25" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
         <v>20.4</v>
@@ -4913,22 +4980,22 @@
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA25" t="n">
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.3</v>
+        <v>104.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4940,10 +5007,10 @@
         <v>6</v>
       </c>
       <c r="AI25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
         <v>12</v>
@@ -4961,13 +5028,13 @@
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR25" t="n">
         <v>13</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>12</v>
       </c>
       <c r="AS25" t="n">
         <v>14</v>
@@ -4997,10 +5064,10 @@
         <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
         <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.647</v>
+        <v>0.657</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J26" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8</v>
+        <v>0.799</v>
       </c>
       <c r="R26" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S26" t="n">
         <v>35.2</v>
       </c>
       <c r="T26" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
         <v>13.8</v>
@@ -5101,13 +5168,13 @@
         <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.6</v>
+        <v>102.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,10 +5186,10 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
         <v>8</v>
@@ -5131,7 +5198,7 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
         <v>2</v>
@@ -5143,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,10 +5368,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" t="n">
         <v>25</v>
       </c>
       <c r="G28" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,25 +5478,25 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q28" t="n">
         <v>0.775</v>
@@ -5438,16 +5505,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U28" t="n">
         <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W28" t="n">
         <v>7.9</v>
@@ -5456,7 +5523,7 @@
         <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
         <v>19.4</v>
@@ -5471,7 +5538,7 @@
         <v>4.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
@@ -5480,7 +5547,7 @@
         <v>6</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5492,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="AK28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,7 +5568,7 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5525,7 +5592,7 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5662,7 +5729,7 @@
         <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>13</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
@@ -5710,25 +5777,25 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G30" t="n">
-        <v>0.449</v>
+        <v>0.456</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J30" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L30" t="n">
         <v>7.3</v>
@@ -5787,7 +5854,7 @@
         <v>21.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O30" t="n">
         <v>16.7</v>
@@ -5796,16 +5863,16 @@
         <v>23.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S30" t="n">
         <v>32</v>
       </c>
       <c r="T30" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U30" t="n">
         <v>20.1</v>
@@ -5826,16 +5893,16 @@
         <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB30" t="n">
         <v>94.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
         <v>16</v>
@@ -5883,7 +5950,7 @@
         <v>18</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>29</v>
@@ -5895,7 +5962,7 @@
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>1.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
       </c>
       <c r="AF31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
@@ -6032,7 +6099,7 @@
         <v>13</v>
       </c>
       <c r="AI31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
         <v>24</v>
@@ -6083,13 +6150,13 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-21-2014-15</t>
+          <t>2015-03-21</t>
         </is>
       </c>
     </row>
